--- a/CBS.FrontDesk.UI/AppFiles/BulkOperation/BulkOperationFileUpload.xlsx
+++ b/CBS.FrontDesk.UI/AppFiles/BulkOperation/BulkOperationFileUpload.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BORIS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BORIS\source\repos\CBS.FrontDesk.UI\CBS.FrontDesk.UI\AppFiles\BulkOperation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{000C0978-B5AB-41C2-9A3E-82521A1FBE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12B52F5-54A9-4E52-A3D4-F8AC7735FEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6EB23830-41F9-440D-B3CF-7AD30EBE9D42}"/>
   </bookViews>
@@ -90,18 +90,6 @@
     <t>Account Type</t>
   </si>
   <si>
-    <t>Savings</t>
-  </si>
-  <si>
-    <t>Deposite</t>
-  </si>
-  <si>
-    <t>Preference Share</t>
-  </si>
-  <si>
-    <t>Member Share</t>
-  </si>
-  <si>
     <t>John Smith</t>
   </si>
   <si>
@@ -109,6 +97,18 @@
   </si>
   <si>
     <t>003</t>
+  </si>
+  <si>
+    <t>Deposit</t>
+  </si>
+  <si>
+    <t>PreferenceShare</t>
+  </si>
+  <si>
+    <t>MemberShare</t>
+  </si>
+  <si>
+    <t>Saving</t>
   </si>
 </sst>
 </file>
@@ -284,6 +284,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -294,9 +297,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -635,40 +635,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="12"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" ht="15">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="11"/>
+      <c r="C3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" ht="15.6">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:4" ht="15.6">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" ht="17.399999999999999">
       <c r="A6" s="7" t="s">
@@ -697,10 +697,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>150</v>
@@ -711,7 +711,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
@@ -725,7 +725,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>11</v>
@@ -739,7 +739,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>12</v>
@@ -753,7 +753,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>13</v>
@@ -767,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
@@ -781,7 +781,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>15</v>
@@ -795,7 +795,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>16</v>
@@ -809,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>17</v>
@@ -823,7 +823,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>18</v>

--- a/CBS.FrontDesk.UI/AppFiles/BulkOperation/BulkOperationFileUpload.xlsx
+++ b/CBS.FrontDesk.UI/AppFiles/BulkOperation/BulkOperationFileUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BORIS\source\repos\CBS.FrontDesk.UI\CBS.FrontDesk.UI\AppFiles\BulkOperation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BORIS\source\repos\CBSUI\CBS.FrontDesk.UI\AppFiles\BulkOperation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12B52F5-54A9-4E52-A3D4-F8AC7735FEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7415EEA9-7A43-4FA4-BCC3-7566EE98F1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6EB23830-41F9-440D-B3CF-7AD30EBE9D42}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6EB23830-41F9-440D-B3CF-7AD30EBE9D42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -196,7 +196,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -258,12 +258,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -285,19 +296,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -634,40 +656,40 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
+      <c r="C2" s="12"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" spans="1:4" ht="15">
+    <row r="3" spans="1:4" ht="15.6">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15.6">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
+      <c r="C4" s="15"/>
       <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:4" ht="15.6">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="16" t="s">
         <v>6</v>
       </c>
+      <c r="C5" s="17"/>
       <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" ht="17.399999999999999">
@@ -835,11 +857,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CBS.FrontDesk.UI/AppFiles/BulkOperation/BulkOperationFileUpload.xlsx
+++ b/CBS.FrontDesk.UI/AppFiles/BulkOperation/BulkOperationFileUpload.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BORIS\source\repos\CBSUI\CBS.FrontDesk.UI\AppFiles\BulkOperation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7415EEA9-7A43-4FA4-BCC3-7566EE98F1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96392BE6-78C4-446D-94AF-210C7BBE8FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{6EB23830-41F9-440D-B3CF-7AD30EBE9D42}"/>
+    <workbookView xWindow="960" yWindow="-15240" windowWidth="21600" windowHeight="11235" xr2:uid="{6EB23830-41F9-440D-B3CF-7AD30EBE9D42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -274,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -295,11 +295,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -319,6 +314,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -656,41 +657,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.6">
+      <c r="C2" s="10"/>
+      <c r="D2" s="9"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.6" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="13"/>
+      <c r="C3" s="10"/>
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15.6">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="15"/>
-      <c r="D4" s="9"/>
+      <c r="D4" s="12"/>
     </row>
     <row r="5" spans="1:4" ht="15.6">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="10"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="14"/>
     </row>
     <row r="6" spans="1:4" ht="17.399999999999999">
       <c r="A6" s="7" t="s">
@@ -858,10 +859,10 @@
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CBS.FrontDesk.UI/AppFiles/BulkOperation/BulkOperationFileUpload.xlsx
+++ b/CBS.FrontDesk.UI/AppFiles/BulkOperation/BulkOperationFileUpload.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BORIS\source\repos\CBSUI\CBS.FrontDesk.UI\AppFiles\BulkOperation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\broth\source\repos\CBS.FrontDesk.UI\CBS.FrontDesk.UI\AppFiles\BulkOperation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96392BE6-78C4-446D-94AF-210C7BBE8FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2D36F3-A7EC-4281-AAA1-AC0B61F1A0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="-15240" windowWidth="21600" windowHeight="11235" xr2:uid="{6EB23830-41F9-440D-B3CF-7AD30EBE9D42}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6EB23830-41F9-440D-B3CF-7AD30EBE9D42}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
   <si>
     <t>BAPCCUL</t>
   </si>
@@ -109,13 +109,16 @@
   </si>
   <si>
     <t>Saving</t>
+  </si>
+  <si>
+    <t>Branch Code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +178,12 @@
       <name val="Bahnschrift"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -274,7 +283,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -298,29 +307,38 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -637,71 +655,78 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C8AE8E-813A-4D39-A2B6-BF996A319114}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="47.109375" style="6" customWidth="1"/>
     <col min="3" max="3" width="67.33203125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="18.77734375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.399999999999999">
+    <row r="1" spans="1:5" ht="17.399999999999999">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="1:4" ht="15">
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:5" ht="15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10"/>
+      <c r="C2" s="9"/>
       <c r="D2" s="9"/>
-    </row>
-    <row r="3" spans="1:4" ht="15.6" customHeight="1">
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="10"/>
+      <c r="C3" s="9"/>
       <c r="D3" s="9"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.6">
+      <c r="E3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.6">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="12"/>
       <c r="D4" s="12"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.6">
+      <c r="E4" s="13"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.6">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="14"/>
-    </row>
-    <row r="6" spans="1:4" ht="17.399999999999999">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:5" ht="17.399999999999999">
       <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:4" s="5" customFormat="1">
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" s="5" customFormat="1">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -714,8 +739,11 @@
       <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -728,8 +756,11 @@
       <c r="D8" s="3">
         <v>150</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -742,8 +773,11 @@
       <c r="D9" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="3">
         <v>3</v>
       </c>
@@ -756,8 +790,11 @@
       <c r="D10" s="3">
         <v>175</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -770,8 +807,11 @@
       <c r="D11" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -784,8 +824,11 @@
       <c r="D12" s="3">
         <v>125</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -798,8 +841,11 @@
       <c r="D13" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -812,8 +858,11 @@
       <c r="D14" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -826,8 +875,11 @@
       <c r="D15" s="3">
         <v>220</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -840,8 +892,11 @@
       <c r="D16" s="3">
         <v>195</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -854,16 +909,20 @@
       <c r="D17" s="3">
         <v>170</v>
       </c>
+      <c r="E17" s="18" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
   </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>